--- a/dataland-framework-toolbox/inputs/pcaf/pcaf.xlsx
+++ b/dataland-framework-toolbox/inputs/pcaf/pcaf.xlsx
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="86">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -88,6 +88,9 @@
     <t>Mandatory Field</t>
   </si>
   <si>
+    <t>Data Point Type Name Overwrite</t>
+  </si>
+  <si>
     <t>General</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>Deviation| No Deviation</t>
   </si>
   <si>
+    <t>Extended</t>
+  </si>
+  <si>
     <t>Fiscal Year End</t>
   </si>
   <si>
@@ -130,7 +136,13 @@
     <t>MAIN_PCAF_SECTOR</t>
   </si>
   <si>
-    <t>Extended</t>
+    <t>One of the following sectors the company is mainly operating in: "Communication Services"; "Consumer Discretionary"; "Consumer Staples"; "Energy"; "Financials"; "Health Care"; "Industrials"; "Information Technology"; "Materials"; "Public"; "Real estate"; "Utilities";</t>
+  </si>
+  <si>
+    <t>Single-Select Dropdown</t>
+  </si>
+  <si>
+    <t>Communication Services|Consumer Discretionary|Consumer Staples|Energy|Financials|Health Care|Industrials|Information Technology|Materials|Public|Real Estate|Utilities</t>
   </si>
   <si>
     <t>Company exchange status</t>
@@ -139,9 +151,54 @@
     <t>COMPANY_EXCHANGE_STATUS</t>
   </si>
   <si>
+    <t>"Listed" if the company is listed on an exchange - otherwise "Unlisted"</t>
+  </si>
+  <si>
+    <t>Listed | Unlisted</t>
+  </si>
+  <si>
     <t>Company Value</t>
   </si>
   <si>
+    <t>Gross Domestic Product (GDP)</t>
+  </si>
+  <si>
+    <t>GDP_IN_EUR</t>
+  </si>
+  <si>
+    <t>A country’s total economic output in euros. See also Regulation (EU) 2022/1288, Annex I, formula (4). Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicator 15</t>
+  </si>
+  <si>
+    <t>Number</t>
+  </si>
+  <si>
+    <t>Allowed Range: [0, INF]</t>
+  </si>
+  <si>
+    <t>EUR</t>
+  </si>
+  <si>
+    <t>PPP adjusted Gross Domestic Product (GDP)</t>
+  </si>
+  <si>
+    <t>PPP_ADJUSTED_GDP_IN_USD</t>
+  </si>
+  <si>
+    <t>A country’s total economic output, adjusted for differences in purchasing power (PPP) in US-dollar. See also PCAF (2025). The Global GHG Accounting and Reporting Standard Part A: Financed Emissions. Third Edition.</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>Book value of debt</t>
+  </si>
+  <si>
+    <t>BOOK_VALUE_OF_DEBT_IN_EUR</t>
+  </si>
+  <si>
+    <t>Book value of debt in EUR = all debt as listed on the company balance sheet (not to be mixed up with other definitions)</t>
+  </si>
+  <si>
     <t>Listed company</t>
   </si>
   <si>
@@ -154,24 +211,6 @@
     <t>Market capitalization in EUR calculated as: number of shares * price per share</t>
   </si>
   <si>
-    <t>Number</t>
-  </si>
-  <si>
-    <t>Allowed Range: [0, INF]</t>
-  </si>
-  <si>
-    <t>EUR</t>
-  </si>
-  <si>
-    <t>Book value of debt</t>
-  </si>
-  <si>
-    <t>BOOK_VALUE_OF_DEBT_IN_EUR</t>
-  </si>
-  <si>
-    <t>Book value of debt in EUR = all debt as listed on the company balance sheet (not to be mixed up with other definitions)</t>
-  </si>
-  <si>
     <t>Minorities interest</t>
   </si>
   <si>
@@ -181,9 +220,28 @@
     <t>Minorities interest in EUR as potentially listed on the balance sheet for ownerships without control (typically for ownerships of less than 50%)</t>
   </si>
   <si>
+    <t>Enterprise Value</t>
+  </si>
+  <si>
+    <t>ENTERPRISE_VALUE_IN_EUR</t>
+  </si>
+  <si>
+    <t>The enterprise value in EUR, i.e. the sum, at fiscal year-end, of the market capitalisation of ordinary shares, the market capitalisation of preferred shares, the book value of total debt and non-controlling interests, without the deduction of cash or cash equivalents. See also Regulation (EU) 2022/1288, Annex I, top (4) and formula (1)+(2).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2</t>
+  </si>
+  <si>
     <t>Unlisted company</t>
   </si>
   <si>
+    <t>Total equity</t>
+  </si>
+  <si>
+    <t>TOTAL_EQUITY_IN_EUR</t>
+  </si>
+  <si>
+    <t>Total equity in EUR as listed on the balance sheet</t>
+  </si>
+  <si>
     <t>Total equity and debt</t>
   </si>
   <si>
@@ -203,123 +261,49 @@
   </si>
   <si>
     <t>SCOPE_1_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Tonnes</t>
-  </si>
-  <si>
-    <t>Scope 2 GHG emissions (location-based)</t>
-  </si>
-  <si>
-    <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 2 GHG emissions (market-based)</t>
-  </si>
-  <si>
-    <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
-  </si>
-  <si>
-    <t>Scope 3 GHG emissions</t>
-  </si>
-  <si>
-    <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>Single-Select Dropdown</t>
-  </si>
-  <si>
-    <t>Listed | Unlisted</t>
-  </si>
-  <si>
-    <t>"Listed" if the company is listed on an exchange - otherwise "Unlisted"</t>
-  </si>
-  <si>
-    <t>Company Value Estimation</t>
-  </si>
-  <si>
-    <t>ESTIMATED_MARKET_CAPITALIZATION_IN_EUR</t>
-  </si>
-  <si>
-    <t>Estimation of Market capitalization in EUR calculated as: number of shares * price per share</t>
-  </si>
-  <si>
-    <t>EstimatedMarketCapitalizationInEUR</t>
-  </si>
-  <si>
-    <t>ESTIMATED_BOOK_VALUE_OF_DEBT_IN_EUR</t>
-  </si>
-  <si>
-    <t>Estimation of Book value of debt in EUR = all debt as listed on the company balance sheet (not to be mixed up with other definitions)</t>
-  </si>
-  <si>
-    <t>EstimatedBookValueOfDebtInEUR</t>
-  </si>
-  <si>
-    <t>ESTIMATED_MINORITIES_INTEREST_IN_EUR</t>
-  </si>
-  <si>
-    <t>Estimation of Minorities interest in EUR as potentially listed on the balance sheet for ownerships without control (typically for ownerships of less than 50%)</t>
-  </si>
-  <si>
-    <t>EstimatedMinoritiesInterestInEUR</t>
-  </si>
-  <si>
-    <t>ESTIMATED_TOTAL_EQUITY_AND_DEBT_IN_EUR</t>
-  </si>
-  <si>
-    <t>Estimation of Sum of total equity and total debt in EUR as listed on the balance sheet</t>
-  </si>
-  <si>
-    <t>EstimatedTotalEquityAndDebtInEUR</t>
-  </si>
-  <si>
-    <t>Environmental Estimation</t>
-  </si>
-  <si>
-    <t>ESTIMATED_SCOPE_1_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>EstimatedScope1GhgEmissionsInTonnes</t>
-  </si>
-  <si>
-    <t>ESTIMATED_SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
-  </si>
-  <si>
-    <t>EstimatedScope2GhgEmissionsLocationBasedInTonnes</t>
-  </si>
-  <si>
-    <t>ESTIMATED_SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
-  </si>
-  <si>
-    <t>EstimatedScope2GhgEmissionsMarketBasedInTonnes</t>
-  </si>
-  <si>
-    <t>ESTIMATED_SCOPE_3_GHG_EMISSIONS_IN_T</t>
-  </si>
-  <si>
-    <t>EstimatedScope3GhgEmissionsInTonnes</t>
-  </si>
-  <si>
-    <t>Data Point Type Name Overwrite</t>
-  </si>
-  <si>
-    <t>One of the following sectors the company is mainly operating in: "Communication Services"; "Consumer Discretionary"; "Consumer Staples"; "Energy"; "Financials"; "Health Care"; "Industrials"; "Industry"; "Information Technology"; "Materials"; "Real estate"; "Sovereign"; "Utilities";</t>
-  </si>
-  <si>
-    <t>Communication Services|Consumer Discretionary|Consumer Staples|Energy|Financials|Health Care|Industrials|Industry|Information Technology|Materials|Real Estate|Sovereign|Utilities</t>
   </si>
   <si>
     <t>Scope 1 greenhouse gas emissions, namely emissions generated from sources that are controlled by the company that issues the underlying assets (equity share approach preferably used). See also Regulation (EU) 2016/1011 Annex III (1)(e)(i).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Tonnes</t>
+  </si>
+  <si>
+    <t>Scope 2 GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_2_GHG_EMISSIONS_IN_T</t>
+  </si>
+  <si>
+    <t>Scope 2 greenhouse gas emissions, namely emissions from the consumption of purchased electricity, steam, or other sources of energy generated upstream from the company that issues the underlying assets (preferably using the location-based method and equity share approach). See also (EU) 2016/1011 Annex III (1)(e)(ii).
+Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 2 GHG emissions (location-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_2_GHG_EMISSIONS_LOCATION_IN_T</t>
+  </si>
+  <si>
     <t>Scope 2 greenhouse gas emissions computed using the location-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
   </si>
   <si>
+    <t>Scope 2 GHG emissions (market-based)</t>
+  </si>
+  <si>
+    <t>SCOPE_2_GHG_EMISSIONS_MARKET_IN_T</t>
+  </si>
+  <si>
     <t>Scope 2 greenhouse gas emissions computed using the market-based method (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(ii).
 Linked to Regulation (EU) 2022/1288, Annex I, Table 1, Adverse sustainability indicators 1, 2, 3</t>
+  </si>
+  <si>
+    <t>Scope 3 GHG emissions</t>
+  </si>
+  <si>
+    <t>SCOPE_3_GHG_EMISSIONS_IN_T</t>
   </si>
   <si>
     <t>Scope 3 greenhouse gas emissions in tons, i.e., all indirect upstream and downstream emissions that are neither covered by scope 1 ghg emissions nor by scope 2 ghg emissions (equity share approach preferably used). See also (EU) 2016/1011 Annex III (1)(e)(iii).
@@ -568,8 +552,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88872740-29A9-40F2-B082-91B9EBCAB4F9}" name="pcaf" displayName="pcaf" ref="A1:O21" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:O21" xr:uid="{88872740-29A9-40F2-B082-91B9EBCAB4F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88872740-29A9-40F2-B082-91B9EBCAB4F9}" name="pcaf" displayName="pcaf" ref="A1:O18" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:O18" xr:uid="{88872740-29A9-40F2-B082-91B9EBCAB4F9}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{98390CE1-0D17-4424-91A3-E09917989074}" uniqueName="1" name="Field Identifier" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{0CDDE416-A15D-4C75-B137-861C20BFFC57}" uniqueName="2" name="Category" queryTableFieldId="2" dataDxfId="13"/>
@@ -818,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1EF222-4BC7-4189-BBB6-74FE5797088E}">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
@@ -882,7 +866,7 @@
         <v>13</v>
       </c>
       <c r="O1" t="s">
-        <v>85</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -890,43 +874,43 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -934,43 +918,43 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" t="s">
+        <v>26</v>
+      </c>
+      <c r="I3" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+      <c r="K3" t="s">
         <v>22</v>
       </c>
-      <c r="F3" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" t="s">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s">
-        <v>24</v>
-      </c>
-      <c r="I3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" t="s">
-        <v>28</v>
-      </c>
       <c r="L3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -978,43 +962,43 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F4" t="s">
-        <v>86</v>
+        <v>30</v>
       </c>
       <c r="G4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H4" t="s">
-        <v>60</v>
+        <v>31</v>
       </c>
       <c r="I4" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K4" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -1022,43 +1006,43 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="E5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>35</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="J5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -1066,43 +1050,43 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="F6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H6" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I6" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K6" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
@@ -1110,43 +1094,43 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="F7" t="s">
+        <v>46</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
         <v>41</v>
       </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" t="s">
-        <v>36</v>
-      </c>
       <c r="I7" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J7" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K7" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -1154,43 +1138,43 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" t="s">
         <v>42</v>
       </c>
-      <c r="E8" t="s">
+      <c r="J8" t="s">
         <v>43</v>
       </c>
-      <c r="F8" t="s">
-        <v>44</v>
-      </c>
-      <c r="G8" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8" t="s">
-        <v>38</v>
-      </c>
       <c r="K8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
@@ -1198,43 +1182,43 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F9" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H9" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K9" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
@@ -1242,43 +1226,43 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E10" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F10" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J10" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
@@ -1286,43 +1270,43 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D11" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>89</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H11" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K11" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
@@ -1330,43 +1314,43 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E12" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F12" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="G12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I12" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J12" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
@@ -1374,355 +1358,263 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="E13" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="G13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H13" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="I13" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="J13" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="K13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="L13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A14" s="1">
+      <c r="A14">
         <v>13</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>64</v>
+      <c r="B14" t="s">
+        <v>68</v>
+      </c>
+      <c r="C14" t="s">
+        <v>69</v>
+      </c>
+      <c r="D14" t="s">
+        <v>70</v>
+      </c>
+      <c r="E14" t="s">
+        <v>71</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L14" s="3"/>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3"/>
-      <c r="O14" s="5" t="s">
-        <v>66</v>
+        <v>72</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" t="s">
+        <v>73</v>
+      </c>
+      <c r="K14" t="s">
+        <v>22</v>
+      </c>
+      <c r="L14" t="s">
+        <v>19</v>
+      </c>
+      <c r="M14" t="s">
+        <v>19</v>
+      </c>
+      <c r="N14" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A15" s="2">
+      <c r="A15">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>67</v>
+      <c r="B15" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" t="s">
+        <v>75</v>
       </c>
       <c r="F15" t="s">
-        <v>68</v>
-      </c>
-      <c r="G15" s="4"/>
-      <c r="H15" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="6" t="s">
-        <v>69</v>
+        <v>76</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>41</v>
+      </c>
+      <c r="I15" t="s">
+        <v>19</v>
+      </c>
+      <c r="J15" t="s">
+        <v>73</v>
+      </c>
+      <c r="K15" t="s">
+        <v>22</v>
+      </c>
+      <c r="L15" t="s">
+        <v>19</v>
+      </c>
+      <c r="M15" t="s">
+        <v>19</v>
+      </c>
+      <c r="N15" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A16" s="1">
+      <c r="A16">
         <v>15</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="B16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" t="s">
+        <v>78</v>
+      </c>
+      <c r="F16" t="s">
+        <v>79</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="F16" t="s">
-        <v>71</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L16" s="3"/>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="5" t="s">
-        <v>72</v>
+      <c r="J16" t="s">
+        <v>73</v>
+      </c>
+      <c r="K16" t="s">
+        <v>22</v>
+      </c>
+      <c r="L16" t="s">
+        <v>19</v>
+      </c>
+      <c r="M16" t="s">
+        <v>19</v>
+      </c>
+      <c r="N16" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A17" s="2">
+      <c r="A17">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="B17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F17" t="s">
+        <v>82</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>41</v>
+      </c>
+      <c r="I17" t="s">
+        <v>42</v>
+      </c>
+      <c r="J17" t="s">
         <v>73</v>
       </c>
-      <c r="F17" t="s">
-        <v>74</v>
-      </c>
-      <c r="G17" s="4"/>
-      <c r="H17" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="6" t="s">
-        <v>75</v>
+      <c r="K17" t="s">
+        <v>22</v>
+      </c>
+      <c r="L17" t="s">
+        <v>19</v>
+      </c>
+      <c r="M17" t="s">
+        <v>19</v>
+      </c>
+      <c r="N17" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18" s="1">
+      <c r="A18">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>77</v>
+      <c r="B18" t="s">
+        <v>68</v>
+      </c>
+      <c r="C18" t="s">
+        <v>69</v>
+      </c>
+      <c r="D18" t="s">
+        <v>83</v>
+      </c>
+      <c r="E18" t="s">
+        <v>84</v>
       </c>
       <c r="F18" t="s">
-        <v>88</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3"/>
-      <c r="O18" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A19" s="2">
-        <v>18</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F19" t="s">
-        <v>89</v>
-      </c>
-      <c r="G19" s="4"/>
-      <c r="H19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="F20" t="s">
-        <v>90</v>
-      </c>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="L20" s="3"/>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3"/>
-      <c r="O20" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="7">
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F21" t="s">
-        <v>91</v>
-      </c>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="J21" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="K21" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="L21" s="8"/>
-      <c r="M21" s="8"/>
-      <c r="N21" s="8"/>
-      <c r="O21" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J18" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" t="s">
+        <v>22</v>
+      </c>
+      <c r="L18" t="s">
+        <v>19</v>
+      </c>
+      <c r="M18" t="s">
+        <v>19</v>
+      </c>
+      <c r="N18" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/dataland-framework-toolbox/inputs/pcaf/pcaf.xlsx
+++ b/dataland-framework-toolbox/inputs/pcaf/pcaf.xlsx
@@ -94,7 +94,7 @@
     <t>General</t>
   </si>
   <si>
-    <t>Fiscal Year Deviation</t>
+    <t>Fiscal year deviation</t>
   </si>
   <si>
     <t>FISCAL_YEAR_DEVIATION</t>
@@ -115,7 +115,7 @@
     <t>Extended</t>
   </si>
   <si>
-    <t>Fiscal Year End</t>
+    <t>Fiscal year end</t>
   </si>
   <si>
     <t>FISCAL_YEAR_END</t>
@@ -157,10 +157,10 @@
     <t>Listed | Unlisted</t>
   </si>
   <si>
-    <t>Company Value</t>
-  </si>
-  <si>
-    <t>Gross Domestic Product (GDP)</t>
+    <t>Company value</t>
+  </si>
+  <si>
+    <t>Gross domestic product (GDP)</t>
   </si>
   <si>
     <t>GDP_IN_EUR</t>
@@ -178,7 +178,7 @@
     <t>EUR</t>
   </si>
   <si>
-    <t>PPP adjusted Gross Domestic Product (GDP)</t>
+    <t>PPP adjusted gross domestic product (GDP)</t>
   </si>
   <si>
     <t>PPP_ADJUSTED_GDP_IN_USD</t>
@@ -220,7 +220,7 @@
     <t>Minorities interest in EUR as potentially listed on the balance sheet for ownerships without control (typically for ownerships of less than 50%)</t>
   </si>
   <si>
-    <t>Enterprise Value</t>
+    <t>Enterprise value</t>
   </si>
   <si>
     <t>ENTERPRISE_VALUE_IN_EUR</t>

--- a/dataland-framework-toolbox/inputs/pcaf/pcaf.xlsx
+++ b/dataland-framework-toolbox/inputs/pcaf/pcaf.xlsx
@@ -157,7 +157,7 @@
     <t>Listed | Unlisted</t>
   </si>
   <si>
-    <t>Company value</t>
+    <t>Financial</t>
   </si>
   <si>
     <t>Gross domestic product (GDP)</t>

--- a/dataland-framework-toolbox/inputs/pcaf/pcaf.xlsx
+++ b/dataland-framework-toolbox/inputs/pcaf/pcaf.xlsx
@@ -552,8 +552,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88872740-29A9-40F2-B082-91B9EBCAB4F9}" name="pcaf" displayName="pcaf" ref="A1:O18" tableType="queryTable" totalsRowShown="0">
-  <autoFilter ref="A1:O18" xr:uid="{88872740-29A9-40F2-B082-91B9EBCAB4F9}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{88872740-29A9-40F2-B082-91B9EBCAB4F9}" name="pcaf" displayName="pcaf" ref="A1:O17" tableType="queryTable" totalsRowShown="0">
+  <autoFilter ref="A1:O17" xr:uid="{88872740-29A9-40F2-B082-91B9EBCAB4F9}"/>
   <tableColumns count="15">
     <tableColumn id="1" xr3:uid="{98390CE1-0D17-4424-91A3-E09917989074}" uniqueName="1" name="Field Identifier" queryTableFieldId="1"/>
     <tableColumn id="2" xr3:uid="{0CDDE416-A15D-4C75-B137-861C20BFFC57}" uniqueName="2" name="Category" queryTableFieldId="2" dataDxfId="13"/>
@@ -802,7 +802,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B1EF222-4BC7-4189-BBB6-74FE5797088E}">
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="13" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.54296875" bestFit="1" customWidth="1"/>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>37</v>
@@ -1056,13 +1056,13 @@
         <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="F6" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G6" t="s">
         <v>19</v>
@@ -1074,7 +1074,7 @@
         <v>42</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="K6" t="s">
         <v>22</v>
@@ -1091,7 +1091,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>37</v>
@@ -1100,13 +1100,13 @@
         <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F7" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G7" t="s">
         <v>19</v>
@@ -1118,7 +1118,7 @@
         <v>42</v>
       </c>
       <c r="J7" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="K7" t="s">
         <v>22</v>
@@ -1135,22 +1135,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" t="s">
         <v>37</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="E8" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F8" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="G8" t="s">
         <v>19</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
@@ -1188,13 +1188,13 @@
         <v>51</v>
       </c>
       <c r="D9" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="E9" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
         <v>19</v>
@@ -1223,7 +1223,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
         <v>37</v>
@@ -1232,13 +1232,13 @@
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
         <v>19</v>
@@ -1247,7 +1247,7 @@
         <v>41</v>
       </c>
       <c r="I10" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="J10" t="s">
         <v>43</v>
@@ -1267,22 +1267,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E11" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="G11" t="s">
         <v>19</v>
@@ -1291,7 +1291,7 @@
         <v>41</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J11" t="s">
         <v>43</v>
@@ -1311,7 +1311,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
         <v>37</v>
@@ -1320,13 +1320,13 @@
         <v>61</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G12" t="s">
         <v>19</v>
@@ -1355,22 +1355,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="G13" t="s">
         <v>19</v>
@@ -1382,7 +1382,7 @@
         <v>42</v>
       </c>
       <c r="J13" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="K13" t="s">
         <v>22</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>68</v>
@@ -1408,13 +1408,13 @@
         <v>69</v>
       </c>
       <c r="D14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s">
         <v>19</v>
@@ -1423,7 +1423,7 @@
         <v>41</v>
       </c>
       <c r="I14" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s">
         <v>73</v>
@@ -1443,7 +1443,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
         <v>68</v>
@@ -1452,13 +1452,13 @@
         <v>69</v>
       </c>
       <c r="D15" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="E15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
         <v>19</v>
@@ -1467,7 +1467,7 @@
         <v>41</v>
       </c>
       <c r="I15" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="J15" t="s">
         <v>73</v>
@@ -1487,7 +1487,7 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
         <v>68</v>
@@ -1496,13 +1496,13 @@
         <v>69</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E16" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G16" t="s">
         <v>19</v>
@@ -1531,7 +1531,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B17" t="s">
         <v>68</v>
@@ -1540,13 +1540,13 @@
         <v>69</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="E17" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="F17" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G17" t="s">
         <v>19</v>
@@ -1570,50 +1570,6 @@
         <v>19</v>
       </c>
       <c r="N17" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>83</v>
-      </c>
-      <c r="E18" t="s">
-        <v>84</v>
-      </c>
-      <c r="F18" t="s">
-        <v>85</v>
-      </c>
-      <c r="G18" t="s">
-        <v>19</v>
-      </c>
-      <c r="H18" t="s">
-        <v>41</v>
-      </c>
-      <c r="I18" t="s">
-        <v>42</v>
-      </c>
-      <c r="J18" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" t="s">
-        <v>22</v>
-      </c>
-      <c r="L18" t="s">
-        <v>19</v>
-      </c>
-      <c r="M18" t="s">
-        <v>19</v>
-      </c>
-      <c r="N18" t="s">
         <v>19</v>
       </c>
     </row>
